--- a/code_book_data_sci_ai_ml/data/sale_quarterly1.xlsx
+++ b/code_book_data_sci_ai_ml/data/sale_quarterly1.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68619CB-E8D4-43AB-81C9-C301A429C30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22266" windowHeight="12648"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="19">
   <si>
     <t>Sales</t>
   </si>
@@ -75,11 +77,17 @@
   <si>
     <t>Rowๆ Labels</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -158,10 +166,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -180,7 +188,1279 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sale_quarterly1.xlsx]Sheet2!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>US</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ญี่ปุ่น</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ไทย</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-27BB-4A56-9C93-A6F8E027153C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>US</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ญี่ปุ่น</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ไทย</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-27BB-4A56-9C93-A6F8E027153C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>US</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ญี่ปุ่น</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ไทย</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-27BB-4A56-9C93-A6F8E027153C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>US</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ญี่ปุ่น</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ไทย</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-27BB-4A56-9C93-A6F8E027153C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1767806591"/>
+        <c:axId val="1695828271"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1767806591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1695828271"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1695828271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1767806591"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -198,7 +1478,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -244,6 +1523,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -399,7 +1719,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-31BD-4C29-8811-23D1E69CCE35}"/>
             </c:ext>
@@ -535,7 +1855,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -599,12 +1918,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
+  <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
@@ -613,6 +1927,11 @@
         <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
     </c:ext>
   </c:extLst>
 </c:chartSpace>
@@ -658,6 +1977,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -1161,7 +2520,551 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{834D4359-7D46-07A0-189B-1F5ADA3A5D5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1178,7 +3081,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1197,7 +3106,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Author" refreshedDate="43534.765172453706" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="20">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Author" refreshedDate="43534.765172453706" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF02000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B3:E23" sheet="Sheet1"/>
   </cacheSource>
@@ -1206,7 +3115,20 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Sales" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1000"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1000" count="12">
+        <n v="1000"/>
+        <n v="300"/>
+        <n v="400"/>
+        <n v="500"/>
+        <n v="800"/>
+        <n v="700"/>
+        <n v="50"/>
+        <n v="60"/>
+        <n v="900"/>
+        <n v="750"/>
+        <n v="200"/>
+        <n v="250"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Quarter" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4" count="4">
@@ -1234,124 +3156,124 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="20">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="20">
   <r>
     <s v="ณิแนน"/>
-    <n v="1000"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
   </r>
   <r>
     <s v="กอบเกียรติ"/>
-    <n v="300"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="1"/>
   </r>
   <r>
     <s v="Tina"/>
-    <n v="400"/>
+    <x v="2"/>
     <x v="0"/>
     <x v="2"/>
   </r>
   <r>
     <s v="Maria"/>
-    <n v="500"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="3"/>
   </r>
   <r>
     <s v="Bill"/>
-    <n v="800"/>
+    <x v="4"/>
     <x v="0"/>
     <x v="0"/>
   </r>
   <r>
     <s v="ณิแนน"/>
-    <n v="1000"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="2"/>
   </r>
   <r>
     <s v="กอบเกียรติ"/>
-    <n v="500"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
   </r>
   <r>
     <s v="Tina"/>
-    <n v="700"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="2"/>
   </r>
   <r>
     <s v="Maria"/>
-    <n v="50"/>
+    <x v="6"/>
     <x v="1"/>
     <x v="0"/>
   </r>
   <r>
     <s v="Bill"/>
-    <n v="60"/>
+    <x v="7"/>
     <x v="1"/>
     <x v="0"/>
   </r>
   <r>
     <s v="ณิแนน"/>
-    <n v="1000"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
   </r>
   <r>
     <s v="กอบเกียรติ"/>
-    <n v="900"/>
+    <x v="8"/>
     <x v="2"/>
     <x v="1"/>
   </r>
   <r>
     <s v="Tina"/>
-    <n v="750"/>
+    <x v="9"/>
     <x v="2"/>
     <x v="2"/>
   </r>
   <r>
     <s v="Maria"/>
-    <n v="200"/>
+    <x v="10"/>
     <x v="2"/>
     <x v="3"/>
   </r>
   <r>
     <s v="Bill"/>
-    <n v="300"/>
+    <x v="1"/>
     <x v="2"/>
     <x v="2"/>
   </r>
   <r>
     <s v="ณิแนน"/>
-    <n v="1000"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="1"/>
   </r>
   <r>
     <s v="กอบเกียรติ"/>
-    <n v="900"/>
+    <x v="8"/>
     <x v="3"/>
     <x v="1"/>
   </r>
   <r>
     <s v="Tina"/>
-    <n v="250"/>
+    <x v="11"/>
     <x v="3"/>
     <x v="2"/>
   </r>
   <r>
     <s v="Maria"/>
-    <n v="750"/>
+    <x v="9"/>
     <x v="3"/>
     <x v="3"/>
   </r>
   <r>
     <s v="Bill"/>
-    <n v="50"/>
+    <x v="6"/>
     <x v="3"/>
     <x v="0"/>
   </r>
@@ -1359,7 +3281,366 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Rowๆ Labels">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D92EEBB2-BCAB-4295-9245-1552C2FE74FB}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:F9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="13">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="19">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Rowๆ Labels">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -1470,6 +3751,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -1730,29 +4014,185 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC913B72-045F-4F81-B0FC-13940B87AF52}">
+  <dimension ref="A3:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" customWidth="1"/>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.65" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="8">
+        <v>500</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8">
+        <v>200</v>
+      </c>
+      <c r="E5" s="8">
+        <v>750</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1800</v>
+      </c>
+      <c r="C6" s="8">
+        <v>110</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="8">
+        <v>50</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8">
+        <v>300</v>
+      </c>
+      <c r="C7" s="8">
+        <v>500</v>
+      </c>
+      <c r="D7" s="8">
+        <v>900</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1900</v>
+      </c>
+      <c r="F7" s="8">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="8">
+        <v>400</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1700</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1050</v>
+      </c>
+      <c r="E8" s="8">
+        <v>250</v>
+      </c>
+      <c r="F8" s="8">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="8">
+        <v>3000</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2310</v>
+      </c>
+      <c r="D9" s="8">
+        <v>3150</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2950</v>
+      </c>
+      <c r="F9" s="8">
+        <v>11410</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1766,7 +4206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1780,7 +4220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1794,7 +4234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1808,7 +4248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +4262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1836,7 +4276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1850,7 +4290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1864,7 +4304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
@@ -1878,7 +4318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +4332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
@@ -1906,7 +4346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1920,7 +4360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
@@ -1934,7 +4374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
@@ -1948,7 +4388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1962,7 +4402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
@@ -1976,7 +4416,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
@@ -1990,7 +4430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>9</v>
       </c>
@@ -2004,7 +4444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,7 +4458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2032,7 +4472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>7</v>
       </c>
@@ -2052,16 +4492,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:B23"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
@@ -2069,163 +4509,163 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>1800</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>2</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>2310</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>1700</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>3</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>3150</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>1050</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>4</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>2950</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19">
         <v>750</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23">
         <v>11410</v>
       </c>
     </row>
